--- a/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-patient.xlsx
+++ b/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:43:13+00:00</t>
+    <t>2026-09-22T13:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -849,7 +849,7 @@
     <t>NMDP GRID (Global Registration Identifier for Donors)</t>
   </si>
   <si>
-    <t>The NMDP GRID identifier that uniquely identifies a donor. A 32-character uppercase alphanumeric string (0-9 and A-F, no dashes or spaces), e.g. 99D0BA02660443B585D525525EB3F2D2. System: http://nmdp.org/identifier/grid</t>
+    <t>The NMDP GRID identifier that uniquely identifies a donor. A 19-character ISBT 128 identifier composed of a 4-digit Issuing Organization Number (ION), a donor registration number, and check characters, e.g. 6939DKM001392612726. System: http://nmdp.org/identifier/grid</t>
   </si>
   <si>
     <t>Patient.identifier:grid.id</t>

--- a/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-patient.xlsx
+++ b/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$89</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4012" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3342" uniqueCount="639">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T13:14:09+00:00</t>
+    <t>2026-09-24T13:17:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -507,7 +507,7 @@
 </t>
   </si>
   <si>
-    <t>(USCDI) Tribal Affiliation Extension</t>
+    <t>Tribal Affiliation Extension</t>
   </si>
   <si>
     <t>A tribe or band with which a person associates whether or not they are an enrolled member.</t>
@@ -523,9 +523,6 @@
 </t>
   </si>
   <si>
-    <t>Birth Sex Extension</t>
-  </si>
-  <si>
     <t>A code classifying the person's sex assigned at birth  as specified by the [Office of the National Coordinator for Health IT (ONC)](https://www.healthit.gov/newsroom/about-onc).</t>
   </si>
   <si>
@@ -545,9 +542,6 @@
 </t>
   </si>
   <si>
-    <t>(USCDI) Sex Extension</t>
-  </si>
-  <si>
     <t>The US Core Sex Extension is used to reflect the documentation of a person's sex. It aligns with the C-CDA Sex Observation (LOINC 46098-0).</t>
   </si>
   <si>
@@ -561,9 +555,6 @@
 </t>
   </si>
   <si>
-    <t>(USCDI) The individual's gender identity</t>
-  </si>
-  <si>
     <t>An individual's personal sense of being a man, woman, boy, girl, nonbinary, or something else.</t>
   </si>
   <si>
@@ -616,20 +607,13 @@
 </t>
   </si>
   <si>
-    <t>(USCDI) An identifier for this patient</t>
-  </si>
-  <si>
-    <t>An identifier for this patient.</t>
+    <t>Donor identifier</t>
+  </si>
+  <si>
+    <t>An identifier for the donor. May be any of the supported NMDP identifiers (e.g. GRID, Donor source ID). The identifier system distinguishes which identifier type is present.</t>
   </si>
   <si>
     <t>Patients are almost always assigned specific numerical identifiers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:system}
-</t>
-  </si>
-  <si>
-    <t>Slice on identifier system</t>
   </si>
   <si>
     <t>id</t>
@@ -838,84 +822,6 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>Patient.identifier:grid</t>
-  </si>
-  <si>
-    <t>grid</t>
-  </si>
-  <si>
-    <t>NMDP GRID (Global Registration Identifier for Donors)</t>
-  </si>
-  <si>
-    <t>The NMDP GRID identifier that uniquely identifies a donor. A 19-character ISBT 128 identifier composed of a 4-digit Issuing Organization Number (ION), a donor registration number, and check characters, e.g. 6939DKM001392612726. System: http://nmdp.org/identifier/grid</t>
-  </si>
-  <si>
-    <t>Patient.identifier:grid.id</t>
-  </si>
-  <si>
-    <t>Patient.identifier:grid.extension</t>
-  </si>
-  <si>
-    <t>Patient.identifier:grid.use</t>
-  </si>
-  <si>
-    <t>Patient.identifier:grid.type</t>
-  </si>
-  <si>
-    <t>Patient.identifier:grid.system</t>
-  </si>
-  <si>
-    <t>http://nmdp.org/identifier/grid</t>
-  </si>
-  <si>
-    <t>Patient.identifier:grid.value</t>
-  </si>
-  <si>
-    <t>Patient.identifier:grid.period</t>
-  </si>
-  <si>
-    <t>Patient.identifier:grid.assigner</t>
-  </si>
-  <si>
-    <t>Patient.identifier:sourceId</t>
-  </si>
-  <si>
-    <t>sourceId</t>
-  </si>
-  <si>
-    <t>Donor source ID</t>
-  </si>
-  <si>
-    <t>The source identifier for the donor in the originating registry. System: http://nmdp.org/identifier/source-id</t>
-  </si>
-  <si>
-    <t>Patient.identifier:sourceId.id</t>
-  </si>
-  <si>
-    <t>Patient.identifier:sourceId.extension</t>
-  </si>
-  <si>
-    <t>Patient.identifier:sourceId.use</t>
-  </si>
-  <si>
-    <t>Patient.identifier:sourceId.type</t>
-  </si>
-  <si>
-    <t>Patient.identifier:sourceId.system</t>
-  </si>
-  <si>
-    <t>http://nmdp.org/identifier/source-id</t>
-  </si>
-  <si>
-    <t>Patient.identifier:sourceId.value</t>
-  </si>
-  <si>
-    <t>Patient.identifier:sourceId.period</t>
-  </si>
-  <si>
-    <t>Patient.identifier:sourceId.assigner</t>
   </si>
   <si>
     <t>Patient.active</t>
@@ -2418,7 +2324,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO107"/>
+  <dimension ref="A1:AO89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.83984375" customWidth="true" bestFit="true"/>
@@ -3770,7 +3676,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>81</v>
@@ -3887,7 +3793,7 @@
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
@@ -3902,13 +3808,13 @@
         <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3973,7 +3879,7 @@
         <v>140</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>81</v>
@@ -3990,13 +3896,13 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>81</v>
@@ -4006,7 +3912,7 @@
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>81</v>
@@ -4018,13 +3924,13 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4107,13 +4013,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>81</v>
@@ -4123,7 +4029,7 @@
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>81</v>
@@ -4135,16 +4041,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4226,13 +4132,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>81</v>
@@ -4254,13 +4160,13 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4343,14 +4249,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4372,16 +4278,16 @@
         <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -4430,7 +4336,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4460,12 +4366,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4476,7 +4382,7 @@
         <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>90</v>
@@ -4488,17 +4394,17 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -4535,19 +4441,19 @@
         <v>81</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4562,16 +4468,16 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -4579,10 +4485,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4605,13 +4511,13 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4662,7 +4568,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4677,7 +4583,7 @@
         <v>81</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>81</v>
@@ -4694,14 +4600,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4723,13 +4629,13 @@
         <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4770,7 +4676,7 @@
         <v>137</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>81</v>
@@ -4779,7 +4685,7 @@
         <v>138</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4794,7 +4700,7 @@
         <v>140</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>81</v>
@@ -4811,10 +4717,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4840,16 +4746,16 @@
         <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4874,13 +4780,13 @@
         <v>81</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>81</v>
@@ -4898,7 +4804,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4913,7 +4819,7 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
@@ -4930,10 +4836,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4956,19 +4862,19 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4993,13 +4899,13 @@
         <v>81</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -5017,7 +4923,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -5032,7 +4938,7 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>81</v>
@@ -5041,7 +4947,7 @@
         <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -5049,10 +4955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5078,16 +4984,16 @@
         <v>103</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -5100,7 +5006,7 @@
         <v>81</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="U23" t="s" s="2">
         <v>81</v>
@@ -5136,7 +5042,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5151,7 +5057,7 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
@@ -5160,7 +5066,7 @@
         <v>81</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -5168,10 +5074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5194,16 +5100,16 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5217,7 +5123,7 @@
         <v>81</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>81</v>
@@ -5253,7 +5159,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5268,7 +5174,7 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
@@ -5277,7 +5183,7 @@
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -5285,10 +5191,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5311,13 +5217,13 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5368,7 +5274,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5383,7 +5289,7 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>81</v>
@@ -5392,7 +5298,7 @@
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -5400,10 +5306,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5426,16 +5332,16 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5485,7 +5391,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5500,7 +5406,7 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
@@ -5509,58 +5415,60 @@
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I27" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>188</v>
+        <v>258</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="O27" t="s" s="2">
-        <v>191</v>
+        <v>262</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q27" s="2"/>
+      <c r="Q27" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="R27" t="s" s="2">
         <v>81</v>
       </c>
@@ -5604,13 +5512,13 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
@@ -5619,27 +5527,27 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>196</v>
+        <v>265</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5647,31 +5555,35 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5719,31 +5631,31 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>81</v>
+        <v>272</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -5751,21 +5663,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -5777,17 +5689,15 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5824,34 +5734,34 @@
         <v>81</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>81</v>
@@ -5868,46 +5778,44 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>81</v>
+        <v>178</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5931,46 +5839,46 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>81</v>
@@ -5979,7 +5887,7 @@
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5987,10 +5895,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6007,25 +5915,25 @@
         <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>222</v>
+        <v>280</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>223</v>
+        <v>281</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -6050,13 +5958,13 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>226</v>
+        <v>283</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -6074,7 +5982,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>228</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -6089,7 +5997,7 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>218</v>
+        <v>286</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>81</v>
@@ -6098,18 +6006,18 @@
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>229</v>
+        <v>287</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6117,13 +6025,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>81</v>
@@ -6132,19 +6040,19 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>103</v>
+        <v>194</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>231</v>
+        <v>289</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>232</v>
+        <v>290</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>233</v>
+        <v>291</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -6154,10 +6062,10 @@
         <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>271</v>
+        <v>81</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>235</v>
+        <v>81</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>81</v>
@@ -6193,7 +6101,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>236</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6208,7 +6116,7 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
@@ -6217,7 +6125,7 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -6225,18 +6133,18 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>239</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>297</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
@@ -6251,16 +6159,16 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>240</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>241</v>
+        <v>299</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>242</v>
+        <v>300</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6274,7 +6182,7 @@
         <v>81</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>81</v>
@@ -6310,7 +6218,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>244</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6319,13 +6227,13 @@
         <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>245</v>
+        <v>303</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -6334,32 +6242,32 @@
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>246</v>
+        <v>304</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>81</v>
@@ -6368,15 +6276,17 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>249</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6425,22 +6335,22 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
@@ -6449,7 +6359,7 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6457,10 +6367,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6471,7 +6381,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -6483,17 +6393,15 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>255</v>
+        <v>194</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>256</v>
+        <v>314</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6542,13 +6450,13 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>259</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
@@ -6557,7 +6465,7 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>260</v>
+        <v>317</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>81</v>
@@ -6566,22 +6474,20 @@
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6590,10 +6496,10 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>81</v>
@@ -6602,18 +6508,16 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>277</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>278</v>
+        <v>321</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>191</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6661,7 +6565,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>187</v>
+        <v>322</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6676,16 +6580,16 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>195</v>
+        <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>197</v>
+        <v>324</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6693,10 +6597,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>279</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>198</v>
+        <v>325</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6716,19 +6620,21 @@
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>200</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>201</v>
+        <v>327</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6776,7 +6682,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>202</v>
+        <v>329</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6788,10 +6694,10 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>203</v>
+        <v>330</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -6800,7 +6706,7 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>81</v>
+        <v>331</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6808,14 +6714,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>204</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6831,21 +6737,23 @@
         <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>134</v>
+        <v>333</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>205</v>
+        <v>334</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>206</v>
+        <v>335</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6881,19 +6789,19 @@
         <v>81</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>208</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6905,19 +6813,19 @@
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>203</v>
+        <v>338</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6925,10 +6833,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>281</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>209</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6945,26 +6853,22 @@
         <v>81</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6988,13 +6892,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -7012,7 +6916,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7024,10 +6928,10 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>81</v>
@@ -7036,7 +6940,7 @@
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -7044,21 +6948,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>282</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>219</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>178</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -7067,23 +6971,21 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>220</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -7107,46 +7009,46 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7155,7 +7057,7 @@
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
@@ -7163,10 +7065,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>283</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>230</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7189,20 +7091,16 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>231</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -7211,10 +7109,10 @@
         <v>81</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>235</v>
+        <v>81</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -7226,13 +7124,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -7250,7 +7148,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>236</v>
+        <v>348</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7259,13 +7157,13 @@
         <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>81</v>
+        <v>349</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>237</v>
+        <v>350</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
@@ -7274,7 +7172,7 @@
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>238</v>
+        <v>351</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -7282,10 +7180,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>285</v>
+        <v>352</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>239</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7308,18 +7206,20 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>240</v>
+        <v>353</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>241</v>
+        <v>354</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7331,7 +7231,7 @@
         <v>81</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>81</v>
@@ -7367,7 +7267,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>244</v>
+        <v>357</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7382,7 +7282,7 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>245</v>
+        <v>358</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
@@ -7391,18 +7291,18 @@
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>246</v>
+        <v>359</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>286</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>247</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7416,25 +7316,29 @@
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>248</v>
+        <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>249</v>
+        <v>361</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7458,13 +7362,11 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -7482,7 +7384,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>251</v>
+        <v>366</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7497,7 +7399,7 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
@@ -7506,7 +7408,7 @@
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>253</v>
+        <v>367</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
@@ -7514,10 +7416,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>287</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>254</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7540,16 +7442,16 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>255</v>
+        <v>369</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>256</v>
+        <v>370</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>257</v>
+        <v>371</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>258</v>
+        <v>372</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7599,7 +7501,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>259</v>
+        <v>373</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7614,7 +7516,7 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>260</v>
+        <v>198</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
@@ -7623,7 +7525,7 @@
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>261</v>
+        <v>198</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -7631,10 +7533,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>288</v>
+        <v>374</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>288</v>
+        <v>374</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7651,32 +7553,26 @@
         <v>81</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>290</v>
+        <v>375</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q45" t="s" s="2">
-        <v>294</v>
-      </c>
+      <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7720,7 +7616,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>288</v>
+        <v>377</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7735,16 +7631,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>296</v>
+        <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7752,10 +7648,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>297</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>297</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7766,7 +7662,7 @@
         <v>89</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>90</v>
@@ -7778,19 +7674,19 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>298</v>
+        <v>109</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>299</v>
+        <v>379</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>301</v>
+        <v>381</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>302</v>
+        <v>382</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7815,13 +7711,11 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7839,42 +7733,42 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>297</v>
+        <v>378</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>303</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>304</v>
+        <v>162</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>305</v>
+        <v>384</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>306</v>
+        <v>385</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>307</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>307</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7882,31 +7776,35 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>199</v>
+        <v>387</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>200</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7954,7 +7852,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>202</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7966,64 +7864,66 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>203</v>
+        <v>392</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>81</v>
+        <v>394</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>81</v>
+        <v>395</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>308</v>
+        <v>396</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>308</v>
+        <v>396</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>134</v>
+        <v>397</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>205</v>
+        <v>398</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>206</v>
+        <v>399</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -8059,54 +7959,54 @@
         <v>81</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>208</v>
+        <v>396</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>203</v>
+        <v>402</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>309</v>
+        <v>404</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>309</v>
+        <v>404</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8117,31 +8017,31 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>109</v>
+        <v>405</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>310</v>
+        <v>406</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>311</v>
+        <v>407</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>312</v>
+        <v>408</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>313</v>
+        <v>409</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -8166,13 +8066,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>315</v>
+        <v>81</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -8190,13 +8090,13 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>316</v>
+        <v>404</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
@@ -8205,16 +8105,16 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>317</v>
+        <v>410</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>81</v>
+        <v>411</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>318</v>
+        <v>412</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -8222,10 +8122,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>413</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>319</v>
+        <v>413</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8245,23 +8145,19 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>320</v>
+        <v>195</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -8309,7 +8205,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>324</v>
+        <v>197</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8321,10 +8217,10 @@
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>325</v>
+        <v>198</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8333,50 +8229,50 @@
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>327</v>
+        <v>414</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>327</v>
+        <v>414</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>328</v>
+        <v>178</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>329</v>
+        <v>200</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>330</v>
+        <v>201</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>331</v>
+        <v>181</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8414,34 +8310,34 @@
         <v>81</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>332</v>
+        <v>203</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>334</v>
+        <v>198</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>81</v>
@@ -8450,52 +8346,54 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>336</v>
+        <v>415</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>336</v>
+        <v>415</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I52" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>338</v>
+        <v>416</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>339</v>
+        <v>417</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8507,7 +8405,7 @@
         <v>81</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>81</v>
@@ -8519,13 +8417,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8543,22 +8441,22 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>341</v>
+        <v>423</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>342</v>
+        <v>286</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>81</v>
@@ -8567,7 +8465,7 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>343</v>
+        <v>424</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -8575,10 +8473,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>344</v>
+        <v>425</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>344</v>
+        <v>425</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8589,7 +8487,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -8601,15 +8499,17 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>345</v>
+        <v>426</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8622,7 +8522,7 @@
         <v>81</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>81</v>
+        <v>429</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>81</v>
@@ -8634,13 +8534,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8658,13 +8558,13 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>347</v>
+        <v>432</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
@@ -8673,7 +8573,7 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>348</v>
+        <v>286</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>81</v>
@@ -8682,7 +8582,7 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>349</v>
+        <v>433</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8690,10 +8590,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>350</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>350</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8704,7 +8604,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8716,16 +8616,20 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>351</v>
+        <v>435</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8737,7 +8641,7 @@
         <v>81</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>81</v>
@@ -8773,13 +8677,13 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>353</v>
+        <v>439</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
@@ -8788,7 +8692,7 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>354</v>
+        <v>294</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
@@ -8797,18 +8701,18 @@
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>355</v>
+        <v>440</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>356</v>
+        <v>441</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>356</v>
+        <v>441</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8819,10 +8723,10 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>81</v>
@@ -8831,18 +8735,16 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>357</v>
+        <v>442</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>358</v>
+        <v>443</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>359</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8854,7 +8756,7 @@
         <v>81</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>81</v>
@@ -8890,13 +8792,13 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>360</v>
+        <v>445</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
@@ -8905,7 +8807,7 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>361</v>
+        <v>446</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
@@ -8914,32 +8816,32 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>362</v>
+        <v>447</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>448</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>363</v>
+        <v>448</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>81</v>
@@ -8948,20 +8850,16 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>364</v>
+        <v>194</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>365</v>
+        <v>450</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8973,7 +8871,7 @@
         <v>81</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>81</v>
+        <v>452</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>81</v>
@@ -9009,13 +8907,13 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>363</v>
+        <v>453</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
@@ -9024,16 +8922,16 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>369</v>
+        <v>454</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>371</v>
+        <v>455</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -9041,14 +8939,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>456</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>372</v>
+        <v>456</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>81</v>
+        <v>457</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9064,18 +8962,20 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>200</v>
+        <v>458</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -9088,7 +8988,7 @@
         <v>81</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>81</v>
@@ -9124,7 +9024,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>202</v>
+        <v>462</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9136,10 +9036,10 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>203</v>
+        <v>463</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>81</v>
@@ -9148,51 +9048,49 @@
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>81</v>
+        <v>464</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>373</v>
+        <v>465</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>373</v>
+        <v>465</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>181</v>
+        <v>466</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>205</v>
+        <v>467</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9217,46 +9115,46 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>81</v>
+        <v>469</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>81</v>
+        <v>470</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>208</v>
+        <v>471</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>203</v>
+        <v>472</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
@@ -9265,7 +9163,7 @@
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -9273,18 +9171,18 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>374</v>
+        <v>474</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>374</v>
+        <v>474</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>475</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>89</v>
@@ -9299,13 +9197,13 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>375</v>
+        <v>476</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>376</v>
+        <v>477</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9320,7 +9218,7 @@
         <v>81</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>81</v>
+        <v>478</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>81</v>
@@ -9332,13 +9230,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>378</v>
+        <v>81</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9356,7 +9254,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>479</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9365,13 +9263,13 @@
         <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>381</v>
+        <v>480</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
@@ -9380,18 +9278,18 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>382</v>
+        <v>481</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>383</v>
+        <v>482</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>383</v>
+        <v>482</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9399,13 +9297,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>81</v>
@@ -9414,20 +9312,18 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>384</v>
+        <v>483</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>385</v>
+        <v>484</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9475,7 +9371,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>388</v>
+        <v>486</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9490,7 +9386,7 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>389</v>
+        <v>487</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>81</v>
@@ -9499,18 +9395,18 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>390</v>
+        <v>488</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>391</v>
+        <v>489</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>489</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9524,28 +9420,26 @@
         <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>109</v>
+        <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>392</v>
+        <v>490</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>395</v>
+        <v>492</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9558,7 +9452,7 @@
         <v>81</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>81</v>
+        <v>493</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>81</v>
@@ -9570,11 +9464,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9592,7 +9488,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>397</v>
+        <v>494</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9607,7 +9503,7 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
@@ -9616,7 +9512,7 @@
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>398</v>
+        <v>495</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
@@ -9624,10 +9520,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>399</v>
+        <v>496</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>399</v>
+        <v>496</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9647,21 +9543,21 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>400</v>
+        <v>215</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>401</v>
+        <v>497</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9685,13 +9581,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>81</v>
+        <v>500</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9709,7 +9605,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>404</v>
+        <v>496</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9724,16 +9620,16 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>203</v>
+        <v>502</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>203</v>
+        <v>504</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9741,10 +9637,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>405</v>
+        <v>505</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>405</v>
+        <v>505</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9764,19 +9660,23 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>248</v>
+        <v>506</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>406</v>
+        <v>507</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
       </c>
@@ -9824,7 +9724,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>408</v>
+        <v>505</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9839,27 +9739,27 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>361</v>
+        <v>511</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>132</v>
+        <v>512</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>409</v>
+        <v>513</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>409</v>
+        <v>513</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9867,34 +9767,34 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>109</v>
+        <v>514</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>410</v>
+        <v>515</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>411</v>
+        <v>516</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>412</v>
+        <v>517</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>413</v>
+        <v>518</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9919,11 +9819,13 @@
         <v>81</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
@@ -9941,13 +9843,13 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>409</v>
+        <v>513</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
@@ -9956,27 +9858,27 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>163</v>
+        <v>519</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>415</v>
+        <v>198</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>416</v>
+        <v>520</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>417</v>
+        <v>521</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>417</v>
+        <v>521</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9984,34 +9886,34 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>418</v>
+        <v>522</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>419</v>
+        <v>523</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>420</v>
+        <v>524</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>421</v>
+        <v>525</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>422</v>
+        <v>526</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10060,42 +9962,42 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>417</v>
+        <v>521</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>527</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>423</v>
+        <v>528</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>424</v>
+        <v>198</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>426</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>427</v>
+        <v>529</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>427</v>
+        <v>529</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10112,26 +10014,22 @@
         <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>428</v>
+        <v>194</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>429</v>
+        <v>195</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -10179,7 +10077,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>427</v>
+        <v>197</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10191,34 +10089,34 @@
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>433</v>
+        <v>198</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>434</v>
+        <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>435</v>
+        <v>530</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>435</v>
+        <v>530</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>81</v>
+        <v>178</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10228,29 +10126,27 @@
         <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>436</v>
+        <v>134</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>437</v>
+        <v>200</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>438</v>
+        <v>201</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
@@ -10298,7 +10194,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>435</v>
+        <v>203</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10310,19 +10206,19 @@
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>441</v>
+        <v>198</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>443</v>
+        <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
@@ -10330,42 +10226,46 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>444</v>
+        <v>531</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>531</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>200</v>
+        <v>533</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
       </c>
@@ -10413,22 +10313,22 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>202</v>
+        <v>535</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>203</v>
+        <v>132</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
@@ -10445,14 +10345,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10471,18 +10371,18 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>205</v>
+        <v>537</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10506,31 +10406,31 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>81</v>
+        <v>540</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>81</v>
+        <v>541</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>208</v>
+        <v>536</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10542,19 +10442,19 @@
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>203</v>
+        <v>542</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>81</v>
+        <v>543</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>81</v>
@@ -10562,10 +10462,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>446</v>
+        <v>544</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>446</v>
+        <v>544</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10582,25 +10482,23 @@
         <v>81</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>109</v>
+        <v>267</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>447</v>
+        <v>545</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>450</v>
+        <v>547</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -10613,7 +10511,7 @@
         <v>81</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>81</v>
@@ -10625,13 +10523,13 @@
         <v>81</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>452</v>
+        <v>81</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>453</v>
+        <v>81</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>81</v>
@@ -10649,7 +10547,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>454</v>
+        <v>544</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10664,16 +10562,16 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>317</v>
+        <v>273</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>455</v>
+        <v>548</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>81</v>
@@ -10681,10 +10579,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>456</v>
+        <v>549</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>456</v>
+        <v>549</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10695,7 +10593,7 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>81</v>
@@ -10704,21 +10602,23 @@
         <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>109</v>
+        <v>333</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>457</v>
+        <v>550</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>458</v>
+        <v>551</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
       </c>
@@ -10730,7 +10630,7 @@
         <v>81</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>460</v>
+        <v>81</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>81</v>
@@ -10742,13 +10642,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>462</v>
+        <v>81</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10766,13 +10666,13 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>463</v>
+        <v>549</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>81</v>
@@ -10781,16 +10681,16 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>464</v>
+        <v>553</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>81</v>
@@ -10798,10 +10698,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>465</v>
+        <v>554</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>465</v>
+        <v>554</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10821,22 +10721,20 @@
         <v>81</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>199</v>
+        <v>405</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>466</v>
+        <v>555</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>323</v>
+        <v>557</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10849,7 +10747,7 @@
         <v>81</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>469</v>
+        <v>81</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>81</v>
@@ -10885,7 +10783,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>470</v>
+        <v>554</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10900,27 +10798,27 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>325</v>
+        <v>410</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>471</v>
+        <v>558</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>559</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>472</v>
+        <v>559</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10931,28 +10829,30 @@
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>473</v>
+        <v>560</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>474</v>
+        <v>561</v>
       </c>
       <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>562</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10964,7 +10864,7 @@
         <v>81</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>81</v>
@@ -10976,13 +10876,13 @@
         <v>81</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>81</v>
+        <v>563</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>81</v>
@@ -11000,13 +10900,13 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>476</v>
+        <v>559</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>81</v>
@@ -11015,31 +10915,31 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>477</v>
+        <v>162</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>478</v>
+        <v>565</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>566</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>566</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>480</v>
+        <v>81</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11049,25 +10949,27 @@
         <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>481</v>
+        <v>567</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
+        <v>568</v>
       </c>
       <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11079,7 +10981,7 @@
         <v>81</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>81</v>
@@ -11115,7 +11017,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>484</v>
+        <v>566</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11124,22 +11026,22 @@
         <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>485</v>
+        <v>571</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>486</v>
+        <v>572</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>81</v>
@@ -11147,14 +11049,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>487</v>
+        <v>573</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>487</v>
+        <v>573</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11170,20 +11072,18 @@
         <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>489</v>
+        <v>574</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11196,7 +11096,7 @@
         <v>81</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>492</v>
+        <v>81</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>81</v>
@@ -11232,7 +11132,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>493</v>
+        <v>573</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11247,59 +11147,63 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>494</v>
+        <v>576</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>496</v>
+        <v>577</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>496</v>
+        <v>577</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>199</v>
+        <v>522</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>498</v>
+        <v>578</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11323,13 +11227,13 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>500</v>
+        <v>81</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>501</v>
+        <v>81</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -11347,13 +11251,13 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>502</v>
+        <v>577</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>81</v>
@@ -11362,31 +11266,31 @@
         <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>503</v>
+        <v>582</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>81</v>
+        <v>583</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>504</v>
+        <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>505</v>
+        <v>584</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>505</v>
+        <v>584</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>506</v>
+        <v>81</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11396,22 +11300,22 @@
         <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>507</v>
+        <v>195</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>508</v>
+        <v>196</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11426,7 +11330,7 @@
         <v>81</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>509</v>
+        <v>81</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>81</v>
@@ -11462,7 +11366,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>510</v>
+        <v>197</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11474,10 +11378,10 @@
         <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>511</v>
+        <v>198</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>81</v>
@@ -11486,7 +11390,7 @@
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
@@ -11494,21 +11398,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>81</v>
+        <v>178</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
@@ -11517,19 +11421,19 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>514</v>
+        <v>200</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>515</v>
+        <v>201</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>516</v>
+        <v>181</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11579,22 +11483,22 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>517</v>
+        <v>203</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>518</v>
+        <v>198</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>81</v>
@@ -11603,7 +11507,7 @@
         <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>519</v>
+        <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>81</v>
@@ -11611,43 +11515,45 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>520</v>
+        <v>586</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>520</v>
+        <v>586</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>248</v>
+        <v>134</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="O79" t="s" s="2">
-        <v>523</v>
+        <v>182</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -11660,7 +11566,7 @@
         <v>81</v>
       </c>
       <c r="T79" t="s" s="2">
-        <v>524</v>
+        <v>81</v>
       </c>
       <c r="U79" t="s" s="2">
         <v>81</v>
@@ -11696,22 +11602,22 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>361</v>
+        <v>132</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>81</v>
@@ -11720,18 +11626,18 @@
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>526</v>
+        <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>527</v>
+        <v>587</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>527</v>
+        <v>587</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11739,13 +11645,13 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>81</v>
@@ -11754,17 +11660,19 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>528</v>
+        <v>588</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>589</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>590</v>
+      </c>
       <c r="O80" t="s" s="2">
-        <v>530</v>
+        <v>591</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11789,13 +11697,11 @@
         <v>81</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>531</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>532</v>
+        <v>592</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>81</v>
@@ -11813,10 +11719,10 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>527</v>
+        <v>587</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>89</v>
@@ -11828,16 +11734,16 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>533</v>
+        <v>593</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>534</v>
+        <v>594</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>535</v>
+        <v>595</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>81</v>
@@ -11845,10 +11751,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>536</v>
+        <v>596</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>536</v>
+        <v>596</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11871,19 +11777,19 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>537</v>
+        <v>258</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>538</v>
+        <v>597</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>539</v>
+        <v>598</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>540</v>
+        <v>599</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>541</v>
+        <v>600</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>81</v>
@@ -11932,7 +11838,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>536</v>
+        <v>596</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11947,16 +11853,16 @@
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>542</v>
+        <v>601</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>203</v>
+        <v>602</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>543</v>
+        <v>603</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>81</v>
@@ -11964,14 +11870,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>544</v>
+        <v>604</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>544</v>
+        <v>604</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>81</v>
+        <v>605</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11990,20 +11896,18 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>545</v>
+        <v>606</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>546</v>
+        <v>607</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>547</v>
+        <v>608</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>81</v>
       </c>
@@ -12051,7 +11955,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>544</v>
+        <v>604</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12066,27 +11970,27 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>550</v>
+        <v>610</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>551</v>
+        <v>611</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>552</v>
+        <v>612</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>552</v>
+        <v>612</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12097,31 +12001,31 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>553</v>
+        <v>613</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>554</v>
+        <v>614</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>555</v>
+        <v>615</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>556</v>
+        <v>616</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>557</v>
+        <v>617</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -12170,25 +12074,25 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>552</v>
+        <v>612</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>558</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>203</v>
+        <v>618</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
@@ -12202,10 +12106,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>560</v>
+        <v>619</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>560</v>
+        <v>619</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12216,28 +12120,32 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>199</v>
+        <v>522</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>200</v>
+        <v>620</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>621</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
       </c>
@@ -12285,25 +12193,25 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>202</v>
+        <v>619</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>203</v>
+        <v>624</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
@@ -12317,21 +12225,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>561</v>
+        <v>625</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>561</v>
+        <v>625</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -12343,17 +12251,15 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12402,22 +12308,22 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>81</v>
@@ -12434,14 +12340,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>562</v>
+        <v>626</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>562</v>
+        <v>626</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>563</v>
+        <v>178</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12454,26 +12360,24 @@
         <v>81</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>564</v>
+        <v>200</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>565</v>
+        <v>201</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
@@ -12521,7 +12425,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>566</v>
+        <v>203</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12536,7 +12440,7 @@
         <v>140</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>81</v>
@@ -12553,14 +12457,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>567</v>
+        <v>627</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>567</v>
+        <v>627</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12573,23 +12477,25 @@
         <v>81</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>220</v>
+        <v>134</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>568</v>
+        <v>533</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="O87" t="s" s="2">
-        <v>570</v>
+        <v>182</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -12614,13 +12520,13 @@
         <v>81</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>571</v>
+        <v>81</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>572</v>
+        <v>81</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>81</v>
@@ -12638,7 +12544,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12650,19 +12556,19 @@
         <v>81</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>573</v>
+        <v>132</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>574</v>
+        <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>81</v>
@@ -12670,10 +12576,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>575</v>
+        <v>628</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>575</v>
+        <v>628</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12681,7 +12587,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>89</v>
@@ -12693,21 +12599,21 @@
         <v>81</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>298</v>
+        <v>629</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>576</v>
+        <v>630</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12755,10 +12661,10 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>575</v>
+        <v>628</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>89</v>
@@ -12770,16 +12676,16 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>304</v>
+        <v>189</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>579</v>
+        <v>633</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>81</v>
@@ -12787,10 +12693,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>580</v>
+        <v>634</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>580</v>
+        <v>634</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12798,10 +12704,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>81</v>
@@ -12810,23 +12716,19 @@
         <v>81</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>364</v>
+        <v>109</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>581</v>
+        <v>635</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12850,13 +12752,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>81</v>
+        <v>636</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>81</v>
+        <v>637</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -12874,13 +12776,13 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>580</v>
+        <v>634</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>81</v>
@@ -12889,2133 +12791,23 @@
         <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>369</v>
+        <v>638</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>584</v>
+        <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="P92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Y98" s="2"/>
-      <c r="Z98" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO107" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO107">
+  <autoFilter ref="A1:AO89">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15025,7 +12817,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI106">
+  <conditionalFormatting sqref="A2:AI88">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
